--- a/docs/Extras/SD2_S26/Reports-Documents/PCB-Assembly-Test-and-Operation/PCB Assembly.xlsx
+++ b/docs/Extras/SD2_S26/Reports-Documents/PCB-Assembly-Test-and-Operation/PCB Assembly.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="65">
   <si>
     <t>Step</t>
   </si>
@@ -107,6 +107,13 @@
     <t>All points are checked out and working</t>
   </si>
   <si>
+    <t>All points checked and continuity was found</t>
+  </si>
+  <si>
+    <t>Did not assemble due to PCB design 
+not being funtional for intened purpose</t>
+  </si>
+  <si>
     <t>Secure Stencil</t>
   </si>
   <si>
@@ -147,6 +154,12 @@
   </si>
   <si>
     <t>Completed - Abdul B.</t>
+  </si>
+  <si>
+    <t>Completed - Abdul B. and Ethan H.</t>
+  </si>
+  <si>
+    <t>Completed - Abdul B. and Luke M.</t>
   </si>
   <si>
     <t>Heat SMD Solder Joints</t>
@@ -193,8 +206,17 @@
   </si>
   <si>
     <t>Waiting for further testing 
-with computers before 
+with computer engineers before 
 assembly begins</t>
+  </si>
+  <si>
+    <t>Problesm with software integration, 
+could not integrate due to J-Tag connection</t>
+  </si>
+  <si>
+    <t>Problesm with software integration, 
+Could not integrate due to J-Tag connection
+Could not integrate with DevKit</t>
   </si>
   <si>
     <t>Motion Sensor Assembly</t>
@@ -239,6 +261,11 @@
 must be connected as follows:
 Pin1: Negative terminal
 Pin2: Positive terminal</t>
+  </si>
+  <si>
+    <t>Waiting for further testing 
+with computers before 
+assembly begins</t>
   </si>
 </sst>
 </file>
@@ -692,259 +719,367 @@
       <c r="J2" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="K2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="G6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="I6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>27</v>
+      <c r="M6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="E9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>51</v>
+      <c r="L10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
